--- a/data/raw/LM2015.xlsx
+++ b/data/raw/LM2015.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2FEFF40-E1CE-44DC-BCB2-7E29B5F57B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369F5E23-D51E-4898-84E9-FA4D885AEE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" tabRatio="853" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16485" windowWidth="29040" windowHeight="15720" tabRatio="853" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="21" r:id="rId1"/>
@@ -20,12 +20,47 @@
     <sheet name="C8_GTO_SIL" sheetId="29" r:id="rId10"/>
     <sheet name="C9_IND_SIL" sheetId="8" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="401">
   <si>
     <t>FONASA</t>
   </si>
@@ -1238,6 +1273,9 @@
   </si>
   <si>
     <t>1) "Glosario estadísticas de licencias médicas año 2015".</t>
+  </si>
+  <si>
+    <t>Traumatismos, envenenamientos y otros</t>
   </si>
 </sst>
 </file>
@@ -11022,562 +11060,562 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B119"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="142.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="142.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="58" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" s="59"/>
     </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="52" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="53"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="54" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="54" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" s="54" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="54" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="54" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="54" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
       <c r="B13" s="54" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="55"/>
     </row>
-    <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B15" s="52" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" s="53"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="54" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="54" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="54" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="54" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="54" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="54" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="54" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="54" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="54" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="54" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="54" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="54" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="10"/>
     </row>
-    <row r="30" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B30" s="52" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" s="53"/>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="54" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="54" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="54" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" s="54" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="54" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" s="54" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" s="54" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" s="54" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" s="54" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" s="54" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" s="10"/>
     </row>
-    <row r="43" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B43" s="52" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" s="53"/>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" s="54" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" s="54" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B47" s="54" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" s="54" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="54" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="54" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="54" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="54" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="10"/>
     </row>
-    <row r="54" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B54" s="52" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="53"/>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B56" s="54" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="54" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="54" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="54" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="54" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="54" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" s="54" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" s="54" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B64" s="54" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" s="54" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B66" s="54" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B67" s="54" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B68" s="54" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B69" s="54" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B70" s="55"/>
     </row>
-    <row r="71" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B71" s="52" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B72" s="53"/>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B73" s="54" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B74" s="54" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B75" s="54" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="54" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B77" s="54" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B78" s="54" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B79" s="54" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B80" s="54" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" s="54" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" s="54" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B83" s="54" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B84" s="54" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B85" s="54" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B86" s="54" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B87" s="55"/>
     </row>
-    <row r="88" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B88" s="52" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" s="53"/>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B90" s="54" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B91" s="54" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B92" s="54" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B93" s="54" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B94" s="54" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" s="54" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" s="54" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" s="54" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B98" s="54" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" s="54" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="54" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B101" s="54" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B102" s="54" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B103" s="54" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B104" s="55"/>
     </row>
-    <row r="105" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B105" s="52" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" s="53"/>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B107" s="54" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B108" s="54" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B109" s="54" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B110" s="55"/>
     </row>
-    <row r="111" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B111" s="52" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B112" s="53"/>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" s="54" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B114" s="54" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" s="54" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" s="54" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" s="54" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B118" s="54" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B119" s="55"/>
     </row>
   </sheetData>
@@ -11685,30 +11723,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="3" customWidth="1"/>
-    <col min="2" max="5" width="15.6640625" style="6" customWidth="1"/>
-    <col min="6" max="7" width="15.6640625" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="33.109375" style="3"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="5" width="15.7109375" style="6" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="33.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
@@ -11722,7 +11760,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="25">
         <v>2011</v>
       </c>
@@ -11736,7 +11774,7 @@
         <v>602622410.27999997</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="25">
         <v>2012</v>
       </c>
@@ -11750,7 +11788,7 @@
         <v>667136789.00300002</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="25">
         <v>2013</v>
       </c>
@@ -11764,7 +11802,7 @@
         <v>747673288.22099996</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
         <v>2014</v>
       </c>
@@ -11778,7 +11816,7 @@
         <v>871854141.10000002</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="27">
         <v>2015</v>
       </c>
@@ -11792,22 +11830,22 @@
         <v>990991503.74671388</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>64</v>
       </c>
@@ -11821,7 +11859,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="25">
         <v>2011</v>
       </c>
@@ -11835,7 +11873,7 @@
         <v>688194792.53975987</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="25">
         <v>2012</v>
       </c>
@@ -11849,7 +11887,7 @@
         <v>750528887.62837493</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="25">
         <v>2013</v>
       </c>
@@ -11863,7 +11901,7 @@
         <v>816459230.73733211</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="25">
         <v>2014</v>
       </c>
@@ -11877,7 +11915,7 @@
         <v>910215723.30840003</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="27">
         <v>2015</v>
       </c>
@@ -11891,22 +11929,22 @@
         <v>990991503.74671388</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>391</v>
       </c>
@@ -11920,7 +11958,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="31" t="s">
         <v>9</v>
       </c>
@@ -11934,7 +11972,7 @@
         <v>263702425.36101347</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="31" t="s">
         <v>10</v>
       </c>
@@ -11948,7 +11986,7 @@
         <v>203974212.03519553</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="31" t="s">
         <v>11</v>
       </c>
@@ -11962,7 +12000,7 @@
         <v>42070440.10790731</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="31" t="s">
         <v>12</v>
       </c>
@@ -11976,7 +12014,7 @@
         <v>116351294.4053736</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="31" t="s">
         <v>13</v>
       </c>
@@ -11990,7 +12028,7 @@
         <v>12288248.380677734</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="31" t="s">
         <v>31</v>
       </c>
@@ -12004,7 +12042,7 @@
         <v>352604883.45654643</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="29" t="s">
         <v>59</v>
       </c>
@@ -12018,7 +12056,7 @@
         <v>990991503.74671388</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>79</v>
       </c>
@@ -12032,30 +12070,30 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="3" customWidth="1"/>
-    <col min="2" max="4" width="15.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="33.109375" style="3"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="4" width="15.7109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="33.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
@@ -12069,7 +12107,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="25">
         <v>2011</v>
       </c>
@@ -12083,7 +12121,7 @@
         <v>130.18671304007711</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="25">
         <v>2012</v>
       </c>
@@ -12097,7 +12135,7 @@
         <v>135.6626358802036</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="25">
         <v>2013</v>
       </c>
@@ -12111,7 +12149,7 @@
         <v>145.93487504313785</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
         <v>2014</v>
       </c>
@@ -12125,7 +12163,7 @@
         <v>157.86798819179873</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="27">
         <v>2015</v>
       </c>
@@ -12139,17 +12177,17 @@
         <v>169.01044000822043</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>64</v>
       </c>
@@ -12163,7 +12201,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="25">
         <v>2011</v>
       </c>
@@ -12177,7 +12215,7 @@
         <v>7.4658602293560303</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="25">
         <v>2012</v>
       </c>
@@ -12191,7 +12229,7 @@
         <v>7.3286091936743807</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="25">
         <v>2013</v>
       </c>
@@ -12205,7 +12243,7 @@
         <v>7.5287182314574475</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="25">
         <v>2014</v>
       </c>
@@ -12219,7 +12257,7 @@
         <v>7.840940140644963</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="27">
         <v>2015</v>
       </c>
@@ -12233,17 +12271,17 @@
         <v>8.1663292445398792</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>64</v>
       </c>
@@ -12257,7 +12295,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="25">
         <v>2011</v>
       </c>
@@ -12271,7 +12309,7 @@
         <v>17.437603844789148</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="25">
         <v>2012</v>
       </c>
@@ -12285,7 +12323,7 @@
         <v>18.511375391295186</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="25">
         <v>2013</v>
       </c>
@@ -12299,7 +12337,7 @@
         <v>19.383761027657297</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="25">
         <v>2014</v>
       </c>
@@ -12313,7 +12351,7 @@
         <v>20.13380861989506</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="27">
         <v>2015</v>
       </c>
@@ -12327,17 +12365,17 @@
         <v>20.696011016360032</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>64</v>
       </c>
@@ -12351,7 +12389,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="25">
         <v>2011</v>
       </c>
@@ -12365,7 +12403,7 @@
         <v>181.48994098229468</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="25">
         <v>2012</v>
       </c>
@@ -12379,7 +12417,7 @@
         <v>189.93754133060867</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="25">
         <v>2013</v>
       </c>
@@ -12393,7 +12431,7 @@
         <v>202.82428744936459</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="25">
         <v>2014</v>
       </c>
@@ -12407,7 +12445,7 @@
         <v>206.29361980991942</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="27">
         <v>2015</v>
       </c>
@@ -12421,17 +12459,17 @@
         <v>204.08921344181263</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>64</v>
       </c>
@@ -12445,7 +12483,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="25">
         <v>2011</v>
       </c>
@@ -12459,7 +12497,7 @@
         <v>10.407963307213739</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="25">
         <v>2012</v>
       </c>
@@ -12473,7 +12511,7 @@
         <v>10.260585035724851</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="25">
         <v>2013</v>
       </c>
@@ -12487,7 +12525,7 @@
         <v>10.463618859104235</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="25">
         <v>2014</v>
       </c>
@@ -12501,7 +12539,7 @@
         <v>10.246129965001856</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="27">
         <v>2015</v>
       </c>
@@ -12515,17 +12553,17 @@
         <v>9.8612826056423017</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>64</v>
       </c>
@@ -12539,7 +12577,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="25">
         <v>2011</v>
       </c>
@@ -12553,7 +12591,7 @@
         <v>1.8283297447281435E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="25">
         <v>2012</v>
       </c>
@@ -12567,7 +12605,7 @@
         <v>1.7969039187019052E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="25">
         <v>2013</v>
       </c>
@@ -12581,7 +12619,7 @@
         <v>1.8580261887212096E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="25">
         <v>2014</v>
       </c>
@@ -12595,7 +12633,7 @@
         <v>1.9863465643705031E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="27">
         <v>2015</v>
       </c>
@@ -12617,23 +12655,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:J25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="60" t="s">
         <v>396</v>
       </c>
       <c r="C2" s="61"/>
     </row>
-    <row r="3" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
     </row>
-    <row r="4" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
         <v>50</v>
       </c>
@@ -12641,11 +12679,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="18" t="s">
         <v>162</v>
       </c>
@@ -12653,7 +12691,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="18" t="s">
         <v>163</v>
       </c>
@@ -12661,7 +12699,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="18" t="s">
         <v>164</v>
       </c>
@@ -12669,7 +12707,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="18" t="s">
         <v>165</v>
       </c>
@@ -12677,7 +12715,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="18" t="s">
         <v>166</v>
       </c>
@@ -12685,7 +12723,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="18" t="s">
         <v>167</v>
       </c>
@@ -12693,7 +12731,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="18" t="s">
         <v>168</v>
       </c>
@@ -12701,7 +12739,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="18" t="s">
         <v>169</v>
       </c>
@@ -12709,7 +12747,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="18" t="s">
         <v>170</v>
       </c>
@@ -12717,7 +12755,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="18" t="s">
         <v>40</v>
       </c>
@@ -12725,7 +12763,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="18" t="s">
         <v>45</v>
       </c>
@@ -12733,7 +12771,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="s">
         <v>205</v>
       </c>
@@ -12741,7 +12779,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">
         <v>173</v>
       </c>
@@ -12749,7 +12787,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="s">
         <v>42</v>
       </c>
@@ -12757,7 +12795,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="s">
         <v>43</v>
       </c>
@@ -12765,7 +12803,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="s">
         <v>41</v>
       </c>
@@ -12773,7 +12811,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="s">
         <v>44</v>
       </c>
@@ -12781,11 +12819,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="19"/>
       <c r="C23" s="10"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="57" t="s">
         <v>397</v>
       </c>
@@ -12793,7 +12831,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J25" s="56" t="s">
         <v>398</v>
       </c>
@@ -12814,37 +12852,37 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="3" customWidth="1"/>
-    <col min="2" max="3" width="15.6640625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="33.33203125" style="3" customWidth="1"/>
-    <col min="6" max="7" width="32.88671875" style="3" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="32.88671875" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="33.109375" style="3"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="33.28515625" style="3" customWidth="1"/>
+    <col min="6" max="7" width="32.85546875" style="3" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="32.85546875" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="33.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>172</v>
       </c>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
@@ -12858,7 +12896,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="25">
         <v>2011</v>
       </c>
@@ -12872,7 +12910,7 @@
         <v>5286213.75</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="25">
         <v>2012</v>
       </c>
@@ -12886,7 +12924,7 @@
         <v>5532318.333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="25">
         <v>2013</v>
       </c>
@@ -12900,7 +12938,7 @@
         <v>5594682.083333333</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
         <v>2014</v>
       </c>
@@ -12914,7 +12952,7 @@
         <v>5765676.333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="27">
         <v>2015</v>
       </c>
@@ -12928,17 +12966,17 @@
         <v>5863492.833333334</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>65</v>
       </c>
@@ -12952,7 +12990,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
         <v>5</v>
       </c>
@@ -12966,7 +13004,7 @@
         <v>3416430.2732665883</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="25" t="s">
         <v>6</v>
       </c>
@@ -12980,7 +13018,7 @@
         <v>2447062.1434000782</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
         <v>59</v>
       </c>
@@ -12994,23 +13032,23 @@
         <v>5863492.416666666</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="28"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="28"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>66</v>
       </c>
@@ -13024,7 +13062,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="22" t="s">
         <v>52</v>
       </c>
@@ -13038,7 +13076,7 @@
         <v>79422.171169936861</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="s">
         <v>2</v>
       </c>
@@ -13052,7 +13090,7 @@
         <v>517520.67958160513</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="25" t="s">
         <v>53</v>
       </c>
@@ -13066,7 +13104,7 @@
         <v>1594750.2596921762</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="25" t="s">
         <v>54</v>
       </c>
@@ -13080,7 +13118,7 @@
         <v>1413937.0903059894</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="25" t="s">
         <v>55</v>
       </c>
@@ -13094,7 +13132,7 @@
         <v>1268307.3747057186</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="25" t="s">
         <v>56</v>
       </c>
@@ -13108,7 +13146,7 @@
         <v>774541.21690266673</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="s">
         <v>3</v>
       </c>
@@ -13122,7 +13160,7 @@
         <v>215013.62430857375</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="29" t="s">
         <v>59</v>
       </c>
@@ -13136,17 +13174,17 @@
         <v>5863492.416666667</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>67</v>
       </c>
@@ -13160,7 +13198,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="22" t="s">
         <v>32</v>
       </c>
@@ -13174,7 +13212,7 @@
         <v>5695756.333333334</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="25" t="s">
         <v>4</v>
       </c>
@@ -13188,7 +13226,7 @@
         <v>167736.08333333331</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="29" t="s">
         <v>59</v>
       </c>
@@ -13202,17 +13240,17 @@
         <v>5863492.416666667</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>392</v>
       </c>
@@ -13226,7 +13264,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="30" t="s">
         <v>14</v>
       </c>
@@ -13240,7 +13278,7 @@
         <v>58551.14881635012</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="31" t="s">
         <v>15</v>
       </c>
@@ -13254,7 +13292,7 @@
         <v>103579.08956988546</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="31" t="s">
         <v>16</v>
       </c>
@@ -13268,7 +13306,7 @@
         <v>221923.26404564435</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="31" t="s">
         <v>17</v>
       </c>
@@ -13282,7 +13320,7 @@
         <v>101160.09241211973</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="31" t="s">
         <v>18</v>
       </c>
@@ -13296,7 +13334,7 @@
         <v>222417.96983986723</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="31" t="s">
         <v>19</v>
       </c>
@@ -13310,7 +13348,7 @@
         <v>554340.25159379141</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
         <v>20</v>
       </c>
@@ -13324,7 +13362,7 @@
         <v>2652219.9247729606</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="31" t="s">
         <v>21</v>
       </c>
@@ -13338,7 +13376,7 @@
         <v>299474.8303399377</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="31" t="s">
         <v>22</v>
       </c>
@@ -13352,7 +13390,7 @@
         <v>310078.0302098454</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="31" t="s">
         <v>23</v>
       </c>
@@ -13366,7 +13404,7 @@
         <v>617974.95829765871</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="31" t="s">
         <v>24</v>
       </c>
@@ -13380,7 +13418,7 @@
         <v>258512.74750729927</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="31" t="s">
         <v>25</v>
       </c>
@@ -13394,7 +13432,7 @@
         <v>101561.92371173309</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="31" t="s">
         <v>26</v>
       </c>
@@ -13408,7 +13446,7 @@
         <v>266548.60664594109</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="31" t="s">
         <v>27</v>
       </c>
@@ -13422,7 +13460,7 @@
         <v>32639.93167391578</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="31" t="s">
         <v>28</v>
       </c>
@@ -13436,7 +13474,7 @@
         <v>62509.647229716778</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="29" t="s">
         <v>59</v>
       </c>
@@ -13450,17 +13488,17 @@
         <v>5863492.416666666</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A65" s="32" t="s">
         <v>68</v>
       </c>
@@ -13474,7 +13512,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="31" t="s">
         <v>57</v>
       </c>
@@ -13488,7 +13526,7 @@
         <v>1162986.9792398275</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="31" t="s">
         <v>69</v>
       </c>
@@ -13502,7 +13540,7 @@
         <v>974105.5711205136</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="31" t="s">
         <v>70</v>
       </c>
@@ -13516,7 +13554,7 @@
         <v>1031689.3057067516</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="31" t="s">
         <v>71</v>
       </c>
@@ -13530,7 +13568,7 @@
         <v>1012624.0199506725</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="31" t="s">
         <v>72</v>
       </c>
@@ -13544,7 +13582,7 @@
         <v>553346.38255440432</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="31" t="s">
         <v>73</v>
       </c>
@@ -13558,7 +13596,7 @@
         <v>309666.40494465403</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="31" t="s">
         <v>74</v>
       </c>
@@ -13572,7 +13610,7 @@
         <v>201874.86920449912</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="31" t="s">
         <v>75</v>
       </c>
@@ -13586,7 +13624,7 @@
         <v>247060.00234457376</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="31" t="s">
         <v>76</v>
       </c>
@@ -13600,7 +13638,7 @@
         <v>370138.88160077034</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="29" t="s">
         <v>59</v>
       </c>
@@ -13614,17 +13652,17 @@
         <v>5863492.416666666</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="32" t="s">
         <v>393</v>
       </c>
@@ -13638,7 +13676,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="31" t="s">
         <v>33</v>
       </c>
@@ -13652,7 +13690,7 @@
         <v>598294.54447039787</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="31" t="s">
         <v>34</v>
       </c>
@@ -13666,7 +13704,7 @@
         <v>81138.893914181172</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="31" t="s">
         <v>35</v>
       </c>
@@ -13680,7 +13718,7 @@
         <v>614466.49814542034</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="31" t="s">
         <v>36</v>
       </c>
@@ -13694,7 +13732,7 @@
         <v>30594.978774772335</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="31" t="s">
         <v>37</v>
       </c>
@@ -13708,7 +13746,7 @@
         <v>737095.91709950392</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="31" t="s">
         <v>38</v>
       </c>
@@ -13722,7 +13760,7 @@
         <v>1117281.8671724538</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="31" t="s">
         <v>39</v>
       </c>
@@ -13736,7 +13774,7 @@
         <v>374934.06391815358</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="31" t="s">
         <v>62</v>
       </c>
@@ -13750,7 +13788,7 @@
         <v>2309686.0698384508</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="29" t="s">
         <v>59</v>
       </c>
@@ -13764,17 +13802,17 @@
         <v>5863492.833333334</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
         <v>64</v>
       </c>
@@ -13788,7 +13826,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="25">
         <v>2011</v>
       </c>
@@ -13802,7 +13840,7 @@
         <v>32960269449.076027</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="25">
         <v>2012</v>
       </c>
@@ -13816,7 +13854,7 @@
         <v>37127015087.425705</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="25">
         <v>2013</v>
       </c>
@@ -13830,7 +13868,7 @@
         <v>40240191056.488159</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="25">
         <v>2014</v>
       </c>
@@ -13844,7 +13882,7 @@
         <v>43892347727.160141</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="27">
         <v>2015</v>
       </c>
@@ -13867,22 +13905,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="3" customWidth="1"/>
-    <col min="2" max="5" width="15.6640625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="6" customWidth="1"/>
-    <col min="7" max="9" width="15.6640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="33.109375" style="3"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="5" width="15.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" style="6" customWidth="1"/>
+    <col min="7" max="9" width="15.7109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="33.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>125</v>
       </c>
@@ -13893,7 +13931,7 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>180</v>
       </c>
@@ -13904,7 +13942,7 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
@@ -13930,7 +13968,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="25">
         <v>2011</v>
       </c>
@@ -13956,7 +13994,7 @@
         <v>46093741</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="25">
         <v>2012</v>
       </c>
@@ -13982,7 +14020,7 @@
         <v>47160567</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="25">
         <v>2013</v>
       </c>
@@ -14008,7 +14046,7 @@
         <v>49519029</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
         <v>2014</v>
       </c>
@@ -14034,7 +14072,7 @@
         <v>50287969</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="27">
         <v>2015</v>
       </c>
@@ -14060,7 +14098,7 @@
         <v>56775616</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>126</v>
       </c>
@@ -14068,7 +14106,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -14076,7 +14114,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>65</v>
       </c>
@@ -14102,7 +14140,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
         <v>5</v>
       </c>
@@ -14128,7 +14166,7 @@
         <v>23859970</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="25" t="s">
         <v>6</v>
       </c>
@@ -14154,7 +14192,7 @@
         <v>32915646</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
         <v>59</v>
       </c>
@@ -14180,7 +14218,7 @@
         <v>56775616</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>197</v>
       </c>
@@ -14188,7 +14226,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>98</v>
       </c>
@@ -14196,7 +14234,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>66</v>
       </c>
@@ -14222,7 +14260,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="22" t="s">
         <v>52</v>
       </c>
@@ -14248,7 +14286,7 @@
         <v>310941.82373410626</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="s">
         <v>2</v>
       </c>
@@ -14274,7 +14312,7 @@
         <v>3585630.0304155946</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="25" t="s">
         <v>53</v>
       </c>
@@ -14300,7 +14338,7 @@
         <v>15592533.45323302</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="25" t="s">
         <v>54</v>
       </c>
@@ -14326,7 +14364,7 @@
         <v>13635597.975426877</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="25" t="s">
         <v>55</v>
       </c>
@@ -14352,7 +14390,7 @@
         <v>12054340.701046262</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="25" t="s">
         <v>56</v>
       </c>
@@ -14378,7 +14416,7 @@
         <v>9080294.2576870285</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="s">
         <v>3</v>
       </c>
@@ -14404,7 +14442,7 @@
         <v>2516277.7584571089</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="29" t="s">
         <v>59</v>
       </c>
@@ -14430,7 +14468,7 @@
         <v>56775616</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>198</v>
       </c>
@@ -14438,7 +14476,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>100</v>
       </c>
@@ -14446,7 +14484,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>67</v>
       </c>
@@ -14472,7 +14510,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="22" t="s">
         <v>29</v>
       </c>
@@ -14498,7 +14536,7 @@
         <v>48188626</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="25" t="s">
         <v>30</v>
       </c>
@@ -14524,7 +14562,7 @@
         <v>8218597</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="25" t="s">
         <v>4</v>
       </c>
@@ -14550,7 +14588,7 @@
         <v>368393</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="29" t="s">
         <v>59</v>
       </c>
@@ -14576,7 +14614,7 @@
         <v>56775616</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
         <v>199</v>
       </c>
@@ -14584,7 +14622,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>102</v>
       </c>
@@ -14592,7 +14630,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>392</v>
       </c>
@@ -14618,7 +14656,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="30" t="s">
         <v>14</v>
       </c>
@@ -14644,7 +14682,7 @@
         <v>395235.5103830006</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="31" t="s">
         <v>15</v>
       </c>
@@ -14670,7 +14708,7 @@
         <v>1067832.8436010797</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="31" t="s">
         <v>16</v>
       </c>
@@ -14696,7 +14734,7 @@
         <v>2154129.8116717893</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="31" t="s">
         <v>17</v>
       </c>
@@ -14722,7 +14760,7 @@
         <v>1061944.7726382888</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="31" t="s">
         <v>18</v>
       </c>
@@ -14748,7 +14786,7 @@
         <v>1614540.3327357515</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
         <v>19</v>
       </c>
@@ -14774,7 +14812,7 @@
         <v>4394569.8824821785</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="31" t="s">
         <v>20</v>
       </c>
@@ -14800,7 +14838,7 @@
         <v>30447342.252815288</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="31" t="s">
         <v>21</v>
       </c>
@@ -14826,7 +14864,7 @@
         <v>3867738.893027653</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="31" t="s">
         <v>22</v>
       </c>
@@ -14852,7 +14890,7 @@
         <v>2143952.4905132577</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="31" t="s">
         <v>23</v>
       </c>
@@ -14878,7 +14916,7 @@
         <v>5112248.9493537396</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="31" t="s">
         <v>24</v>
       </c>
@@ -14904,7 +14942,7 @@
         <v>1797974.6932919081</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="31" t="s">
         <v>25</v>
       </c>
@@ -14930,7 +14968,7 @@
         <v>384307.39502100786</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="31" t="s">
         <v>26</v>
       </c>
@@ -14956,7 +14994,7 @@
         <v>1587993.8936299311</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="31" t="s">
         <v>27</v>
       </c>
@@ -14982,7 +15020,7 @@
         <v>202920.92840032643</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="31" t="s">
         <v>28</v>
       </c>
@@ -15008,7 +15046,7 @@
         <v>542883.35043480014</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="29" t="s">
         <v>59</v>
       </c>
@@ -15034,7 +15072,7 @@
         <v>56775616</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
         <v>215</v>
       </c>
@@ -15042,7 +15080,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
         <v>104</v>
       </c>
@@ -15050,7 +15088,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
         <v>394</v>
       </c>
@@ -15076,7 +15114,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="31" t="s">
         <v>60</v>
       </c>
@@ -15102,7 +15140,7 @@
         <v>46183527</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="31" t="s">
         <v>61</v>
       </c>
@@ -15128,7 +15166,7 @@
         <v>4115470</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="31" t="s">
         <v>7</v>
       </c>
@@ -15154,7 +15192,7 @@
         <v>6476504</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="31" t="s">
         <v>8</v>
       </c>
@@ -15176,7 +15214,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="29" t="s">
         <v>59</v>
       </c>
@@ -15210,24 +15248,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I186"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="3" customWidth="1"/>
-    <col min="2" max="5" width="15.6640625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="6" customWidth="1"/>
-    <col min="7" max="11" width="15.6640625" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="33.109375" style="3"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="5" width="15.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" style="6" customWidth="1"/>
+    <col min="7" max="11" width="15.7109375" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="33.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>212</v>
       </c>
@@ -15238,7 +15276,7 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>183</v>
       </c>
@@ -15249,7 +15287,7 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
@@ -15257,7 +15295,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>58</v>
@@ -15275,7 +15313,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="25">
         <v>2011</v>
       </c>
@@ -15301,7 +15339,7 @@
         <v>39466133</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="25">
         <v>2012</v>
       </c>
@@ -15327,7 +15365,7 @@
         <v>40544199</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="25">
         <v>2013</v>
       </c>
@@ -15353,7 +15391,7 @@
         <v>42120785</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
         <v>2014</v>
       </c>
@@ -15379,7 +15417,7 @@
         <v>45208323</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="27">
         <v>2015</v>
       </c>
@@ -15405,7 +15443,7 @@
         <v>47883213</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>79</v>
       </c>
@@ -15413,10 +15451,10 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>129</v>
       </c>
@@ -15424,7 +15462,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>106</v>
       </c>
@@ -15432,7 +15470,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>65</v>
       </c>
@@ -15440,7 +15478,7 @@
         <v>0</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>58</v>
@@ -15458,7 +15496,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
         <v>5</v>
       </c>
@@ -15484,7 +15522,7 @@
         <v>20923920.952536896</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="25" t="s">
         <v>6</v>
       </c>
@@ -15510,7 +15548,7 @@
         <v>26959292.047463104</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
         <v>59</v>
       </c>
@@ -15536,7 +15574,7 @@
         <v>47883213</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>79</v>
       </c>
@@ -15544,10 +15582,10 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>209</v>
       </c>
@@ -15555,7 +15593,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>107</v>
       </c>
@@ -15563,7 +15601,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>66</v>
       </c>
@@ -15571,7 +15609,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>58</v>
@@ -15589,7 +15627,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="22" t="s">
         <v>52</v>
       </c>
@@ -15615,7 +15653,7 @@
         <v>232173.58776425439</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="s">
         <v>2</v>
       </c>
@@ -15641,7 +15679,7 @@
         <v>2808961.5606066743</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="25" t="s">
         <v>53</v>
       </c>
@@ -15667,7 +15705,7 @@
         <v>12565745.841647789</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="25" t="s">
         <v>54</v>
       </c>
@@ -15693,7 +15731,7 @@
         <v>11456291.001890579</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="25" t="s">
         <v>55</v>
       </c>
@@ -15719,7 +15757,7 @@
         <v>10527435.863646081</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="25" t="s">
         <v>56</v>
       </c>
@@ -15745,7 +15783,7 @@
         <v>8021585.3675880209</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="s">
         <v>3</v>
       </c>
@@ -15771,7 +15809,7 @@
         <v>2271019.7768566036</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="29" t="s">
         <v>59</v>
       </c>
@@ -15797,7 +15835,7 @@
         <v>47883213</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>79</v>
       </c>
@@ -15805,10 +15843,10 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>210</v>
       </c>
@@ -15816,7 +15854,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>109</v>
       </c>
@@ -15824,7 +15862,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>67</v>
       </c>
@@ -15832,7 +15870,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>58</v>
@@ -15850,7 +15888,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="22" t="s">
         <v>29</v>
       </c>
@@ -15876,7 +15914,7 @@
         <v>41612834.519381069</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="25" t="s">
         <v>30</v>
       </c>
@@ -15902,7 +15940,7 @@
         <v>5928729.4967057016</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="25" t="s">
         <v>4</v>
       </c>
@@ -15928,7 +15966,7 @@
         <v>341648.9839132285</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="29" t="s">
         <v>59</v>
       </c>
@@ -15954,7 +15992,7 @@
         <v>47883213</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>79</v>
       </c>
@@ -15962,10 +16000,10 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>247</v>
       </c>
@@ -15973,7 +16011,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>111</v>
       </c>
@@ -15981,7 +16019,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>392</v>
       </c>
@@ -15989,7 +16027,7 @@
         <v>0</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>58</v>
@@ -16007,7 +16045,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="30" t="s">
         <v>14</v>
       </c>
@@ -16033,7 +16071,7 @@
         <v>329316.61186307267</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="31" t="s">
         <v>15</v>
       </c>
@@ -16059,7 +16097,7 @@
         <v>849097.7763280404</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="31" t="s">
         <v>16</v>
       </c>
@@ -16085,7 +16123,7 @@
         <v>1861113.0158535927</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="31" t="s">
         <v>17</v>
       </c>
@@ -16111,7 +16149,7 @@
         <v>900564.60412711743</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="31" t="s">
         <v>18</v>
       </c>
@@ -16137,7 +16175,7 @@
         <v>1366725.0618064329</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
         <v>19</v>
       </c>
@@ -16163,7 +16201,7 @@
         <v>3727581.8938781056</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="31" t="s">
         <v>20</v>
       </c>
@@ -16189,7 +16227,7 @@
         <v>25706041.401552837</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="31" t="s">
         <v>21</v>
       </c>
@@ -16215,7 +16253,7 @@
         <v>3352947.6541295853</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="31" t="s">
         <v>22</v>
       </c>
@@ -16241,7 +16279,7 @@
         <v>1839363.4731822908</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="31" t="s">
         <v>23</v>
       </c>
@@ -16267,7 +16305,7 @@
         <v>4343645.8802470081</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="31" t="s">
         <v>24</v>
       </c>
@@ -16293,7 +16331,7 @@
         <v>1439218.7102826866</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="31" t="s">
         <v>25</v>
       </c>
@@ -16319,7 +16357,7 @@
         <v>293112.77639865485</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="31" t="s">
         <v>26</v>
       </c>
@@ -16345,7 +16383,7 @@
         <v>1263019.0602074279</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="31" t="s">
         <v>27</v>
       </c>
@@ -16371,7 +16409,7 @@
         <v>160358.37996117855</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="31" t="s">
         <v>28</v>
       </c>
@@ -16397,7 +16435,7 @@
         <v>451106.70018196927</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="29" t="s">
         <v>59</v>
       </c>
@@ -16423,7 +16461,7 @@
         <v>47883212.999999985</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>79</v>
       </c>
@@ -16431,15 +16469,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F63" s="3"/>
     </row>
-    <row r="74" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -16450,22 +16488,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="3" customWidth="1"/>
-    <col min="2" max="5" width="20.6640625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="6" customWidth="1"/>
-    <col min="7" max="9" width="20.6640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="33.109375" style="3"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="5" width="20.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" style="6" customWidth="1"/>
+    <col min="7" max="9" width="20.7109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="33.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>134</v>
       </c>
@@ -16476,7 +16514,7 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>184</v>
       </c>
@@ -16487,7 +16525,7 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
@@ -16513,7 +16551,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="25">
         <v>2011</v>
       </c>
@@ -16539,7 +16577,7 @@
         <v>5520701</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="25">
         <v>2012</v>
       </c>
@@ -16565,7 +16603,7 @@
         <v>6226468</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="25">
         <v>2013</v>
       </c>
@@ -16591,7 +16629,7 @@
         <v>6420918</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
         <v>2014</v>
       </c>
@@ -16617,7 +16655,7 @@
         <v>5599347</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="27">
         <v>2015</v>
       </c>
@@ -16643,13 +16681,13 @@
         <v>6476504</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>135</v>
       </c>
@@ -16657,7 +16695,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>113</v>
       </c>
@@ -16665,7 +16703,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>65</v>
       </c>
@@ -16691,7 +16729,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
         <v>5</v>
       </c>
@@ -16717,7 +16755,7 @@
         <v>2868079</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="25" t="s">
         <v>6</v>
       </c>
@@ -16743,7 +16781,7 @@
         <v>3608425</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
         <v>59</v>
       </c>
@@ -16769,13 +16807,13 @@
         <v>6476504</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>213</v>
       </c>
@@ -16783,7 +16821,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>114</v>
       </c>
@@ -16791,7 +16829,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>66</v>
       </c>
@@ -16817,7 +16855,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="22" t="s">
         <v>52</v>
       </c>
@@ -16843,7 +16881,7 @@
         <v>17254.415608302705</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="s">
         <v>2</v>
       </c>
@@ -16869,7 +16907,7 @@
         <v>316764.62993156019</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="25" t="s">
         <v>53</v>
       </c>
@@ -16895,7 +16933,7 @@
         <v>1970785.4704459982</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="25" t="s">
         <v>54</v>
       </c>
@@ -16921,7 +16959,7 @@
         <v>1676075.3717434579</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="25" t="s">
         <v>55</v>
       </c>
@@ -16947,7 +16985,7 @@
         <v>1224070.4842704562</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="25" t="s">
         <v>56</v>
       </c>
@@ -16973,7 +17011,7 @@
         <v>1022694.6337164093</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="s">
         <v>3</v>
       </c>
@@ -16999,7 +17037,7 @@
         <v>248858.9942838155</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="29" t="s">
         <v>59</v>
       </c>
@@ -17025,13 +17063,13 @@
         <v>6476504</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>251</v>
       </c>
@@ -17039,7 +17077,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>115</v>
       </c>
@@ -17047,7 +17085,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>392</v>
       </c>
@@ -17073,7 +17111,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="30" t="s">
         <v>14</v>
       </c>
@@ -17099,7 +17137,7 @@
         <v>20824.703638460567</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="31" t="s">
         <v>15</v>
       </c>
@@ -17125,7 +17163,7 @@
         <v>177681.8268524211</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="31" t="s">
         <v>16</v>
       </c>
@@ -17151,7 +17189,7 @@
         <v>277577.70541745721</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="31" t="s">
         <v>17</v>
       </c>
@@ -17177,7 +17215,7 @@
         <v>120408.09572651701</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="31" t="s">
         <v>18</v>
       </c>
@@ -17203,7 +17241,7 @@
         <v>150976.32932138204</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="31" t="s">
         <v>19</v>
       </c>
@@ -17229,7 +17267,7 @@
         <v>507720.97165029566</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="31" t="s">
         <v>20</v>
       </c>
@@ -17255,7 +17293,7 @@
         <v>3389227.3213004884</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="31" t="s">
         <v>21</v>
       </c>
@@ -17281,7 +17319,7 @@
         <v>494941.28276272106</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="31" t="s">
         <v>22</v>
       </c>
@@ -17307,7 +17345,7 @@
         <v>160707.76302706471</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="31" t="s">
         <v>23</v>
       </c>
@@ -17333,7 +17371,7 @@
         <v>644211.03271143674</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="31" t="s">
         <v>24</v>
       </c>
@@ -17359,7 +17397,7 @@
         <v>229593.89484589032</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="31" t="s">
         <v>25</v>
       </c>
@@ -17385,7 +17423,7 @@
         <v>45768.180647691741</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="31" t="s">
         <v>26</v>
       </c>
@@ -17411,7 +17449,7 @@
         <v>163430.42746036168</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="31" t="s">
         <v>27</v>
       </c>
@@ -17437,7 +17475,7 @@
         <v>23688.490996845121</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
         <v>28</v>
       </c>
@@ -17463,7 +17501,7 @@
         <v>69745.973640966418</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="29" t="s">
         <v>59</v>
       </c>
@@ -17489,10 +17527,10 @@
         <v>6476503.9999999991</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F54" s="3"/>
     </row>
   </sheetData>
@@ -17505,36 +17543,36 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Q842"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="3" customWidth="1"/>
-    <col min="2" max="5" width="15.6640625" style="6" customWidth="1"/>
-    <col min="6" max="8" width="15.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" style="3" customWidth="1"/>
-    <col min="11" max="17" width="15.6640625" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="33.109375" style="3"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="5" width="15.7109375" style="6" customWidth="1"/>
+    <col min="6" max="8" width="15.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" style="3" customWidth="1"/>
+    <col min="11" max="17" width="15.7109375" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="33.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>391</v>
       </c>
@@ -17548,7 +17586,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="31" t="s">
         <v>9</v>
       </c>
@@ -17562,7 +17600,7 @@
         <v>1056960</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="31" t="s">
         <v>10</v>
       </c>
@@ -17576,7 +17614,7 @@
         <v>981162</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="31" t="s">
         <v>11</v>
       </c>
@@ -17590,7 +17628,7 @@
         <v>710702</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="31" t="s">
         <v>12</v>
       </c>
@@ -17604,7 +17642,7 @@
         <v>355051</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="31" t="s">
         <v>13</v>
       </c>
@@ -17618,7 +17656,7 @@
         <v>296490</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
         <v>31</v>
       </c>
@@ -17632,7 +17670,7 @@
         <v>1344492</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
         <v>59</v>
       </c>
@@ -17646,7 +17684,7 @@
         <v>4744857</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>263</v>
       </c>
@@ -17658,7 +17696,7 @@
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>139</v>
       </c>
@@ -17670,7 +17708,7 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="46" t="s">
         <v>65</v>
       </c>
@@ -17720,7 +17758,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="22" t="s">
         <v>5</v>
       </c>
@@ -17770,7 +17808,7 @@
         <v>657941</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="s">
         <v>6</v>
       </c>
@@ -17820,7 +17858,7 @@
         <v>745031</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
         <v>59</v>
       </c>
@@ -17870,19 +17908,19 @@
         <v>1402972</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>265</v>
       </c>
@@ -17894,7 +17932,7 @@
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>142</v>
       </c>
@@ -17906,7 +17944,7 @@
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
         <v>66</v>
       </c>
@@ -17956,7 +17994,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="22" t="s">
         <v>52</v>
       </c>
@@ -18006,7 +18044,7 @@
         <v>2854.0793380724526</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="25" t="s">
         <v>2</v>
       </c>
@@ -18056,7 +18094,7 @@
         <v>69770.939501743851</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="25" t="s">
         <v>53</v>
       </c>
@@ -18106,7 +18144,7 @@
         <v>505031.03891917859</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="25" t="s">
         <v>54</v>
       </c>
@@ -18156,7 +18194,7 @@
         <v>396054.00956139748</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="s">
         <v>55</v>
       </c>
@@ -18206,7 +18244,7 @@
         <v>241504.71337975512</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="25" t="s">
         <v>56</v>
       </c>
@@ -18256,7 +18294,7 @@
         <v>160841.47109234723</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="25" t="s">
         <v>3</v>
       </c>
@@ -18306,7 +18344,7 @@
         <v>26915.748207505276</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="29" t="s">
         <v>59</v>
       </c>
@@ -18356,19 +18394,19 @@
         <v>1402972</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>266</v>
       </c>
@@ -18380,7 +18418,7 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>143</v>
       </c>
@@ -18392,7 +18430,7 @@
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A38" s="24" t="s">
         <v>392</v>
       </c>
@@ -18442,7 +18480,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="30" t="s">
         <v>14</v>
       </c>
@@ -18492,7 +18530,7 @@
         <v>9552.7316668658204</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="31" t="s">
         <v>15</v>
       </c>
@@ -18542,7 +18580,7 @@
         <v>26897.923164743024</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="31" t="s">
         <v>16</v>
       </c>
@@ -18592,7 +18630,7 @@
         <v>67105.440434320029</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="31" t="s">
         <v>17</v>
       </c>
@@ -18642,7 +18680,7 @@
         <v>17048.278176166819</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="31" t="s">
         <v>18</v>
       </c>
@@ -18692,7 +18730,7 @@
         <v>17295.705944258807</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="31" t="s">
         <v>19</v>
       </c>
@@ -18742,7 +18780,7 @@
         <v>73452.720117822697</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="31" t="s">
         <v>20</v>
       </c>
@@ -18792,7 +18830,7 @@
         <v>903648.62526076043</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="31" t="s">
         <v>21</v>
       </c>
@@ -18842,7 +18880,7 @@
         <v>45606.492160269969</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="31" t="s">
         <v>22</v>
       </c>
@@ -18892,7 +18930,7 @@
         <v>31742.457873058422</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="31" t="s">
         <v>23</v>
       </c>
@@ -18942,7 +18980,7 @@
         <v>94837.548645773204</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="31" t="s">
         <v>24</v>
       </c>
@@ -18992,7 +19030,7 @@
         <v>36747.568153319233</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="31" t="s">
         <v>25</v>
       </c>
@@ -19042,7 +19080,7 @@
         <v>14241.740349523398</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
         <v>26</v>
       </c>
@@ -19092,7 +19130,7 @@
         <v>46108.417061256572</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="31" t="s">
         <v>27</v>
       </c>
@@ -19142,7 +19180,7 @@
         <v>5169.725489236298</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="31" t="s">
         <v>28</v>
       </c>
@@ -19192,7 +19230,7 @@
         <v>13516.62550262524</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="29" t="s">
         <v>59</v>
       </c>
@@ -19242,19 +19280,19 @@
         <v>1402972.0000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
         <v>269</v>
       </c>
@@ -19263,7 +19301,7 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
         <v>276</v>
       </c>
@@ -19273,7 +19311,7 @@
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>391</v>
       </c>
@@ -19292,7 +19330,7 @@
       <c r="M59" s="35"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="31" t="s">
         <v>9</v>
       </c>
@@ -19311,7 +19349,7 @@
       <c r="M60" s="17"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="31" t="s">
         <v>10</v>
       </c>
@@ -19330,7 +19368,7 @@
       <c r="M61" s="17"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="31" t="s">
         <v>11</v>
       </c>
@@ -19349,7 +19387,7 @@
       <c r="M62" s="17"/>
       <c r="N62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="31" t="s">
         <v>12</v>
       </c>
@@ -19368,7 +19406,7 @@
       <c r="M63" s="17"/>
       <c r="N63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="31" t="s">
         <v>13</v>
       </c>
@@ -19387,7 +19425,7 @@
       <c r="M64" s="17"/>
       <c r="N64" s="6"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="31" t="s">
         <v>31</v>
       </c>
@@ -19406,7 +19444,7 @@
       <c r="M65" s="17"/>
       <c r="N65" s="6"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="29" t="s">
         <v>59</v>
       </c>
@@ -19425,19 +19463,19 @@
       <c r="M66" s="17"/>
       <c r="N66" s="6"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
         <v>270</v>
       </c>
@@ -19449,7 +19487,7 @@
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
         <v>277</v>
       </c>
@@ -19461,7 +19499,7 @@
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
-    <row r="71" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A71" s="46" t="s">
         <v>65</v>
       </c>
@@ -19511,7 +19549,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="22" t="s">
         <v>5</v>
       </c>
@@ -19561,7 +19599,7 @@
         <v>6757494</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="25" t="s">
         <v>6</v>
       </c>
@@ -19611,7 +19649,7 @@
         <v>7440631</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="29" t="s">
         <v>59</v>
       </c>
@@ -19661,19 +19699,19 @@
         <v>14198125</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
         <v>271</v>
       </c>
@@ -19685,7 +19723,7 @@
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
         <v>279</v>
       </c>
@@ -19697,7 +19735,7 @@
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
-    <row r="79" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A79" s="24" t="s">
         <v>66</v>
       </c>
@@ -19747,7 +19785,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="22" t="s">
         <v>52</v>
       </c>
@@ -19797,7 +19835,7 @@
         <v>20732.486255609321</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="25" t="s">
         <v>2</v>
       </c>
@@ -19847,7 +19885,7 @@
         <v>550582.91326214664</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="25" t="s">
         <v>53</v>
       </c>
@@ -19897,7 +19935,7 @@
         <v>4482974.1427839622</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="25" t="s">
         <v>54</v>
       </c>
@@ -19947,7 +19985,7 @@
         <v>3977220.2809334719</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="25" t="s">
         <v>55</v>
       </c>
@@ -19997,7 +20035,7 @@
         <v>2688509.0557566979</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="25" t="s">
         <v>56</v>
       </c>
@@ -20047,7 +20085,7 @@
         <v>2074985.6663011401</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="25" t="s">
         <v>3</v>
       </c>
@@ -20097,7 +20135,7 @@
         <v>403120.45470697136</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="29" t="s">
         <v>59</v>
       </c>
@@ -20147,19 +20185,19 @@
         <v>14198124.999999998</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
         <v>272</v>
       </c>
@@ -20171,7 +20209,7 @@
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
         <v>281</v>
       </c>
@@ -20183,7 +20221,7 @@
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A92" s="24" t="s">
         <v>392</v>
       </c>
@@ -20233,7 +20271,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="30" t="s">
         <v>14</v>
       </c>
@@ -20283,7 +20321,7 @@
         <v>83912.881647687755</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="31" t="s">
         <v>15</v>
       </c>
@@ -20333,7 +20371,7 @@
         <v>321801.17091649631</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="31" t="s">
         <v>16</v>
       </c>
@@ -20383,7 +20421,7 @@
         <v>768017.2658974122</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="31" t="s">
         <v>17</v>
       </c>
@@ -20433,7 +20471,7 @@
         <v>213159.98257877753</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="31" t="s">
         <v>18</v>
       </c>
@@ -20483,7 +20521,7 @@
         <v>208985.08676939987</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="31" t="s">
         <v>19</v>
       </c>
@@ -20533,7 +20571,7 @@
         <v>826072.04438331712</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="31" t="s">
         <v>20</v>
       </c>
@@ -20583,7 +20621,7 @@
         <v>8621645.4872075599</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="31" t="s">
         <v>21</v>
       </c>
@@ -20633,7 +20671,7 @@
         <v>573351.01162344019</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="31" t="s">
         <v>22</v>
       </c>
@@ -20683,7 +20721,7 @@
         <v>334583.31866661034</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="31" t="s">
         <v>23</v>
       </c>
@@ -20733,7 +20771,7 @@
         <v>1088372.620417529</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="31" t="s">
         <v>24</v>
       </c>
@@ -20783,7 +20821,7 @@
         <v>388050.25517964654</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="31" t="s">
         <v>25</v>
       </c>
@@ -20833,7 +20871,7 @@
         <v>123354.79332685082</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="31" t="s">
         <v>26</v>
       </c>
@@ -20883,7 +20921,7 @@
         <v>437467.49227517034</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="31" t="s">
         <v>27</v>
       </c>
@@ -20933,7 +20971,7 @@
         <v>49815.038534192419</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="31" t="s">
         <v>28</v>
       </c>
@@ -20983,7 +21021,7 @@
         <v>159536.55057590976</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="29" t="s">
         <v>59</v>
       </c>
@@ -21033,95 +21071,95 @@
         <v>14198125.000000004</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -21131,36 +21169,36 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Q842"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="3" customWidth="1"/>
-    <col min="2" max="5" width="15.6640625" style="6" customWidth="1"/>
-    <col min="6" max="8" width="15.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" style="3" customWidth="1"/>
-    <col min="11" max="17" width="15.6640625" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="33.109375" style="3"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="5" width="15.7109375" style="6" customWidth="1"/>
+    <col min="6" max="8" width="15.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" style="3" customWidth="1"/>
+    <col min="11" max="17" width="15.7109375" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="33.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>391</v>
       </c>
@@ -21168,13 +21206,13 @@
         <v>0</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="31" t="s">
         <v>9</v>
       </c>
@@ -21188,7 +21226,7 @@
         <v>929735.63134126912</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="31" t="s">
         <v>10</v>
       </c>
@@ -21202,7 +21240,7 @@
         <v>980790.42479177483</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="31" t="s">
         <v>11</v>
       </c>
@@ -21216,9 +21254,9 @@
         <v>797378.95014518034</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="31" t="s">
-        <v>12</v>
+        <v>400</v>
       </c>
       <c r="B9" s="5">
         <v>242979</v>
@@ -21230,7 +21268,7 @@
         <v>375773.12122783426</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="31" t="s">
         <v>13</v>
       </c>
@@ -21244,7 +21282,7 @@
         <v>330543.46085717645</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
         <v>31</v>
       </c>
@@ -21258,7 +21296,7 @@
         <v>1441456.4116367651</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
         <v>59</v>
       </c>
@@ -21272,12 +21310,12 @@
         <v>4855678</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>291</v>
       </c>
@@ -21289,7 +21327,7 @@
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>146</v>
       </c>
@@ -21301,27 +21339,28 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="46" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="F17" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="46" t="s">
-        <v>395</v>
+      <c r="B17" s="46" t="str" cm="1">
+        <f t="array" ref="B17:G17">TRANSPOSE(A6:A11)</f>
+        <v>Trastornos mentales</v>
+      </c>
+      <c r="C17" s="46" t="str">
+        <v>Enf. osteomusculares</v>
+      </c>
+      <c r="D17" s="46" t="str">
+        <v>Enf. respiratorias</v>
+      </c>
+      <c r="E17" s="46" t="str">
+        <v>Traumatismos, envenenamientos y otros</v>
+      </c>
+      <c r="F17" s="46" t="str">
+        <v>Enf. infecciosas</v>
+      </c>
+      <c r="G17" s="46" t="str">
+        <v>Otros diagnósticos</v>
       </c>
       <c r="H17" s="46" t="s">
         <v>63</v>
@@ -21330,28 +21369,28 @@
         <v>65</v>
       </c>
       <c r="K17" s="46" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="L17" s="46" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="M17" s="46" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="N17" s="46" t="s">
-        <v>161</v>
+        <v>400</v>
       </c>
       <c r="O17" s="46" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="P17" s="46" t="s">
-        <v>395</v>
+        <v>31</v>
       </c>
       <c r="Q17" s="46" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="22" t="s">
         <v>5</v>
       </c>
@@ -21401,7 +21440,7 @@
         <v>801611.83725802239</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="s">
         <v>6</v>
       </c>
@@ -21451,7 +21490,7 @@
         <v>895008.16274197761</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
         <v>59</v>
       </c>
@@ -21501,7 +21540,7 @@
         <v>1696620</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J21" s="3" t="s">
         <v>79</v>
       </c>
@@ -21510,13 +21549,13 @@
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>292</v>
       </c>
@@ -21528,7 +21567,7 @@
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>149</v>
       </c>
@@ -21540,27 +21579,27 @@
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
         <v>66</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="C25" s="46" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="D25" s="46" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>161</v>
+        <v>400</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="G25" s="46" t="s">
-        <v>395</v>
+        <v>31</v>
       </c>
       <c r="H25" s="46" t="s">
         <v>63</v>
@@ -21569,28 +21608,28 @@
         <v>66</v>
       </c>
       <c r="K25" s="46" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="L25" s="46" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="M25" s="46" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="N25" s="46" t="s">
-        <v>161</v>
+        <v>400</v>
       </c>
       <c r="O25" s="46" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="P25" s="46" t="s">
-        <v>395</v>
+        <v>31</v>
       </c>
       <c r="Q25" s="46" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="22" t="s">
         <v>52</v>
       </c>
@@ -21640,7 +21679,7 @@
         <v>3420.0687277201805</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="25" t="s">
         <v>2</v>
       </c>
@@ -21690,7 +21729,7 @@
         <v>84049.10835703733</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="25" t="s">
         <v>53</v>
       </c>
@@ -21740,7 +21779,7 @@
         <v>611824.55293635104</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="25" t="s">
         <v>54</v>
       </c>
@@ -21790,7 +21829,7 @@
         <v>476113.73644036427</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="s">
         <v>55</v>
       </c>
@@ -21840,7 +21879,7 @@
         <v>294062.26166220376</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="25" t="s">
         <v>56</v>
       </c>
@@ -21890,7 +21929,7 @@
         <v>194672.3487473281</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="25" t="s">
         <v>3</v>
       </c>
@@ -21940,7 +21979,7 @@
         <v>32477.92312899536</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="29" t="s">
         <v>59</v>
       </c>
@@ -21990,7 +22029,7 @@
         <v>1696620</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J34" s="3" t="s">
         <v>79</v>
       </c>
@@ -21999,13 +22038,13 @@
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>293</v>
       </c>
@@ -22017,7 +22056,7 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>150</v>
       </c>
@@ -22029,27 +22068,27 @@
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A38" s="24" t="s">
         <v>392</v>
       </c>
       <c r="B38" s="46" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="C38" s="46" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>161</v>
+        <v>400</v>
       </c>
       <c r="F38" s="46" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="G38" s="46" t="s">
-        <v>395</v>
+        <v>31</v>
       </c>
       <c r="H38" s="46" t="s">
         <v>63</v>
@@ -22058,28 +22097,28 @@
         <v>392</v>
       </c>
       <c r="K38" s="46" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="L38" s="46" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="M38" s="46" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="N38" s="46" t="s">
-        <v>161</v>
+        <v>400</v>
       </c>
       <c r="O38" s="46" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="P38" s="46" t="s">
-        <v>395</v>
+        <v>31</v>
       </c>
       <c r="Q38" s="46" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="30" t="s">
         <v>14</v>
       </c>
@@ -22129,7 +22168,7 @@
         <v>12123.162050688556</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="31" t="s">
         <v>15</v>
       </c>
@@ -22179,7 +22218,7 @@
         <v>30249.483682894606</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="31" t="s">
         <v>16</v>
       </c>
@@ -22229,7 +22268,7 @@
         <v>79356.269502462019</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="31" t="s">
         <v>17</v>
       </c>
@@ -22279,7 +22318,7 @@
         <v>19638.154605381951</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="31" t="s">
         <v>18</v>
       </c>
@@ -22329,7 +22368,7 @@
         <v>20879.25405838498</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="31" t="s">
         <v>19</v>
       </c>
@@ -22379,7 +22418,7 @@
         <v>87667.788571769299</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="31" t="s">
         <v>20</v>
       </c>
@@ -22429,7 +22468,7 @@
         <v>1098846.0871113471</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="31" t="s">
         <v>21</v>
       </c>
@@ -22479,7 +22518,7 @@
         <v>51520.588888898223</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="31" t="s">
         <v>22</v>
       </c>
@@ -22529,7 +22568,7 @@
         <v>39759.354807282878</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="31" t="s">
         <v>23</v>
       </c>
@@ -22579,7 +22618,7 @@
         <v>115017.57376228605</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="31" t="s">
         <v>24</v>
       </c>
@@ -22629,7 +22668,7 @@
         <v>43727.738247711604</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="31" t="s">
         <v>25</v>
       </c>
@@ -22679,7 +22718,7 @@
         <v>18000.92926496809</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
         <v>26</v>
       </c>
@@ -22729,7 +22768,7 @@
         <v>57607.818352995702</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="31" t="s">
         <v>27</v>
       </c>
@@ -22779,7 +22818,7 @@
         <v>6269.6183618981713</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="31" t="s">
         <v>28</v>
       </c>
@@ -22829,7 +22868,7 @@
         <v>15956.178731030845</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="29" t="s">
         <v>59</v>
       </c>
@@ -22879,7 +22918,7 @@
         <v>1696620</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J55" s="3" t="s">
         <v>79</v>
       </c>
@@ -22888,13 +22927,13 @@
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
         <v>297</v>
       </c>
@@ -22903,7 +22942,7 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
         <v>283</v>
       </c>
@@ -22913,7 +22952,7 @@
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>391</v>
       </c>
@@ -22932,7 +22971,7 @@
       <c r="M59" s="35"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="31" t="s">
         <v>9</v>
       </c>
@@ -22951,7 +22990,7 @@
       <c r="M60" s="17"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="31" t="s">
         <v>10</v>
       </c>
@@ -22970,7 +23009,7 @@
       <c r="M61" s="17"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="31" t="s">
         <v>11</v>
       </c>
@@ -22989,7 +23028,7 @@
       <c r="M62" s="17"/>
       <c r="N62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="31" t="s">
         <v>12</v>
       </c>
@@ -23008,7 +23047,7 @@
       <c r="M63" s="17"/>
       <c r="N63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="31" t="s">
         <v>13</v>
       </c>
@@ -23027,7 +23066,7 @@
       <c r="M64" s="17"/>
       <c r="N64" s="6"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="31" t="s">
         <v>31</v>
       </c>
@@ -23046,7 +23085,7 @@
       <c r="M65" s="17"/>
       <c r="N65" s="6"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="29" t="s">
         <v>59</v>
       </c>
@@ -23065,7 +23104,7 @@
       <c r="M66" s="17"/>
       <c r="N66" s="6"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>79</v>
       </c>
@@ -23074,13 +23113,13 @@
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
         <v>298</v>
       </c>
@@ -23092,7 +23131,7 @@
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
         <v>284</v>
       </c>
@@ -23104,7 +23143,7 @@
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
-    <row r="71" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A71" s="46" t="s">
         <v>65</v>
       </c>
@@ -23154,7 +23193,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="22" t="s">
         <v>5</v>
       </c>
@@ -23204,7 +23243,7 @@
         <v>6213489.9525368959</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="25" t="s">
         <v>6</v>
       </c>
@@ -23254,7 +23293,7 @@
         <v>6097078.0474631041</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="29" t="s">
         <v>59</v>
       </c>
@@ -23304,7 +23343,7 @@
         <v>12310568</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J75" s="3" t="s">
         <v>79</v>
       </c>
@@ -23313,13 +23352,13 @@
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
         <v>299</v>
       </c>
@@ -23331,7 +23370,7 @@
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
         <v>286</v>
       </c>
@@ -23343,7 +23382,7 @@
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
-    <row r="79" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A79" s="24" t="s">
         <v>66</v>
       </c>
@@ -23393,7 +23432,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="22" t="s">
         <v>52</v>
       </c>
@@ -23443,7 +23482,7 @@
         <v>14879.091260079873</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="25" t="s">
         <v>2</v>
       </c>
@@ -23493,7 +23532,7 @@
         <v>413939.14545548474</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="25" t="s">
         <v>53</v>
       </c>
@@ -23543,7 +23582,7 @@
         <v>3602159.958459178</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="25" t="s">
         <v>54</v>
       </c>
@@ -23593,7 +23632,7 @@
         <v>3421277.2749143941</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="25" t="s">
         <v>55</v>
       </c>
@@ -23643,7 +23682,7 @@
         <v>2506860.6510384874</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="25" t="s">
         <v>56</v>
       </c>
@@ -23693,7 +23732,7 @@
         <v>1950395.1275396838</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="25" t="s">
         <v>3</v>
       </c>
@@ -23743,7 +23782,7 @@
         <v>401056.75133269199</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="29" t="s">
         <v>59</v>
       </c>
@@ -23793,7 +23832,7 @@
         <v>12310568</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J88" s="3" t="s">
         <v>79</v>
       </c>
@@ -23802,13 +23841,13 @@
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
         <v>300</v>
       </c>
@@ -23820,7 +23859,7 @@
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
         <v>288</v>
       </c>
@@ -23832,7 +23871,7 @@
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A92" s="24" t="s">
         <v>392</v>
       </c>
@@ -23882,7 +23921,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="30" t="s">
         <v>14</v>
       </c>
@@ -23932,7 +23971,7 @@
         <v>71273.294523312332</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="31" t="s">
         <v>15</v>
       </c>
@@ -23982,7 +24021,7 @@
         <v>246535.16847273734</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="31" t="s">
         <v>16</v>
       </c>
@@ -24032,7 +24071,7 @@
         <v>713237.91294037818</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="31" t="s">
         <v>17</v>
       </c>
@@ -24082,7 +24121,7 @@
         <v>181030.09523491876</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="31" t="s">
         <v>18</v>
       </c>
@@ -24132,7 +24171,7 @@
         <v>168553.25378615846</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="31" t="s">
         <v>19</v>
       </c>
@@ -24182,7 +24221,7 @@
         <v>715915.06960474188</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="31" t="s">
         <v>20</v>
       </c>
@@ -24232,7 +24271,7 @@
         <v>7476376.3766403412</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="31" t="s">
         <v>21</v>
       </c>
@@ -24282,7 +24321,7 @@
         <v>492962.7208767155</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="31" t="s">
         <v>22</v>
       </c>
@@ -24332,7 +24371,7 @@
         <v>269970.63698483945</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="31" t="s">
         <v>23</v>
       </c>
@@ -24382,7 +24421,7 @@
         <v>1010801.3099550796</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="31" t="s">
         <v>24</v>
       </c>
@@ -24432,7 +24471,7 @@
         <v>304735.59408954607</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="31" t="s">
         <v>25</v>
       </c>
@@ -24482,7 +24521,7 @@
         <v>104520.03724260048</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="31" t="s">
         <v>26</v>
       </c>
@@ -24532,7 +24571,7 @@
         <v>379970.8155750244</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="31" t="s">
         <v>27</v>
       </c>
@@ -24582,7 +24621,7 @@
         <v>38091.121445279729</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="31" t="s">
         <v>28</v>
       </c>
@@ -24632,7 +24671,7 @@
         <v>136594.59262832673</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="29" t="s">
         <v>59</v>
       </c>
@@ -24682,99 +24721,99 @@
         <v>12310568</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J109" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -24784,36 +24823,36 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Q191"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="3" customWidth="1"/>
-    <col min="2" max="5" width="15.6640625" style="6" customWidth="1"/>
-    <col min="6" max="8" width="15.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" style="3" customWidth="1"/>
-    <col min="11" max="17" width="15.6640625" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="33.109375" style="3"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="5" width="15.7109375" style="6" customWidth="1"/>
+    <col min="6" max="8" width="15.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" style="3" customWidth="1"/>
+    <col min="11" max="17" width="15.7109375" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="33.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>391</v>
       </c>
@@ -24827,7 +24866,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="31" t="s">
         <v>9</v>
       </c>
@@ -24841,7 +24880,7 @@
         <v>198491</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="31" t="s">
         <v>10</v>
       </c>
@@ -24855,7 +24894,7 @@
         <v>77133</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="31" t="s">
         <v>11</v>
       </c>
@@ -24869,7 +24908,7 @@
         <v>20900</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="31" t="s">
         <v>12</v>
       </c>
@@ -24883,7 +24922,7 @@
         <v>18183</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="31" t="s">
         <v>13</v>
       </c>
@@ -24897,7 +24936,7 @@
         <v>8808</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
         <v>31</v>
       </c>
@@ -24911,7 +24950,7 @@
         <v>62735</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
         <v>59</v>
       </c>
@@ -24925,7 +24964,7 @@
         <v>386250</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>333</v>
       </c>
@@ -24937,7 +24976,7 @@
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>153</v>
       </c>
@@ -24949,7 +24988,7 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="46" t="s">
         <v>65</v>
       </c>
@@ -24999,7 +25038,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="22" t="s">
         <v>5</v>
       </c>
@@ -25049,7 +25088,7 @@
         <v>91186</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="s">
         <v>6</v>
       </c>
@@ -25099,7 +25138,7 @@
         <v>112243</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
         <v>59</v>
       </c>
@@ -25149,19 +25188,19 @@
         <v>203429</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>334</v>
       </c>
@@ -25173,7 +25212,7 @@
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>156</v>
       </c>
@@ -25185,7 +25224,7 @@
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
         <v>66</v>
       </c>
@@ -25235,7 +25274,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="22" t="s">
         <v>52</v>
       </c>
@@ -25285,7 +25324,7 @@
         <v>436.0257205641613</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="25" t="s">
         <v>2</v>
       </c>
@@ -25335,7 +25374,7 @@
         <v>10346.610332469754</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="25" t="s">
         <v>53</v>
       </c>
@@ -25385,7 +25424,7 @@
         <v>72459.274274028227</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="25" t="s">
         <v>54</v>
       </c>
@@ -25435,7 +25474,7 @@
         <v>59432.505842677849</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="s">
         <v>55</v>
       </c>
@@ -25485,7 +25524,7 @@
         <v>33596.98184025917</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="25" t="s">
         <v>56</v>
       </c>
@@ -25535,7 +25574,7 @@
         <v>23204.368794151917</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="25" t="s">
         <v>3</v>
       </c>
@@ -25585,7 +25624,7 @@
         <v>3953.2331958489212</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="29" t="s">
         <v>59</v>
       </c>
@@ -25635,19 +25674,19 @@
         <v>203428.99999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>335</v>
       </c>
@@ -25659,7 +25698,7 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>157</v>
       </c>
@@ -25671,7 +25710,7 @@
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A38" s="24" t="s">
         <v>392</v>
       </c>
@@ -25721,7 +25760,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="30" t="s">
         <v>14</v>
       </c>
@@ -25771,7 +25810,7 @@
         <v>974.50158923651168</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="31" t="s">
         <v>15</v>
       </c>
@@ -25821,7 +25860,7 @@
         <v>5538.5710723694483</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="31" t="s">
         <v>16</v>
       </c>
@@ -25871,7 +25910,7 @@
         <v>11020.782957138468</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="31" t="s">
         <v>17</v>
       </c>
@@ -25921,7 +25960,7 @@
         <v>3175.5840431587271</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="31" t="s">
         <v>18</v>
       </c>
@@ -25971,7 +26010,7 @@
         <v>2534.1140170156605</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="31" t="s">
         <v>19</v>
       </c>
@@ -26021,7 +26060,7 @@
         <v>11483.953007963813</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="31" t="s">
         <v>20</v>
       </c>
@@ -26071,7 +26110,7 @@
         <v>126669.83591321913</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="31" t="s">
         <v>21</v>
       </c>
@@ -26121,7 +26160,7 @@
         <v>9224.4619414375156</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="31" t="s">
         <v>22</v>
       </c>
@@ -26171,7 +26210,7 @@
         <v>3615.1857064420747</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="31" t="s">
         <v>23</v>
       </c>
@@ -26221,7 +26260,7 @@
         <v>13513.908474081089</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="31" t="s">
         <v>24</v>
       </c>
@@ -26271,7 +26310,7 @@
         <v>5839.8365479062877</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="31" t="s">
         <v>25</v>
       </c>
@@ -26321,7 +26360,7 @@
         <v>1505.3026651823718</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
         <v>26</v>
       </c>
@@ -26371,7 +26410,7 @@
         <v>5356.1722470444229</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="31" t="s">
         <v>27</v>
       </c>
@@ -26421,7 +26460,7 @@
         <v>736.76828881288316</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="31" t="s">
         <v>28</v>
       </c>
@@ -26471,7 +26510,7 @@
         <v>2240.0215289916032</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="29" t="s">
         <v>59</v>
       </c>
@@ -26521,19 +26560,19 @@
         <v>203428.99999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
         <v>346</v>
       </c>
@@ -26542,7 +26581,7 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
         <v>339</v>
       </c>
@@ -26552,7 +26591,7 @@
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>391</v>
       </c>
@@ -26571,7 +26610,7 @@
       <c r="M59" s="35"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="31" t="s">
         <v>9</v>
       </c>
@@ -26590,7 +26629,7 @@
       <c r="M60" s="17"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="31" t="s">
         <v>10</v>
       </c>
@@ -26609,7 +26648,7 @@
       <c r="M61" s="17"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="31" t="s">
         <v>11</v>
       </c>
@@ -26628,7 +26667,7 @@
       <c r="M62" s="17"/>
       <c r="N62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="31" t="s">
         <v>12</v>
       </c>
@@ -26647,7 +26686,7 @@
       <c r="M63" s="17"/>
       <c r="N63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="31" t="s">
         <v>13</v>
       </c>
@@ -26666,7 +26705,7 @@
       <c r="M64" s="17"/>
       <c r="N64" s="6"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="31" t="s">
         <v>31</v>
       </c>
@@ -26685,7 +26724,7 @@
       <c r="M65" s="17"/>
       <c r="N65" s="6"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="29" t="s">
         <v>59</v>
       </c>
@@ -26704,19 +26743,19 @@
       <c r="M66" s="17"/>
       <c r="N66" s="6"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
         <v>347</v>
       </c>
@@ -26728,7 +26767,7 @@
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
         <v>340</v>
       </c>
@@ -26740,7 +26779,7 @@
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
-    <row r="71" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A71" s="46" t="s">
         <v>65</v>
       </c>
@@ -26790,7 +26829,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="22" t="s">
         <v>5</v>
       </c>
@@ -26840,7 +26879,7 @@
         <v>1820926</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="25" t="s">
         <v>6</v>
       </c>
@@ -26890,7 +26929,7 @@
         <v>1352759</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="29" t="s">
         <v>59</v>
       </c>
@@ -26940,19 +26979,19 @@
         <v>3173685</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
         <v>348</v>
       </c>
@@ -26964,7 +27003,7 @@
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
         <v>342</v>
       </c>
@@ -26976,7 +27015,7 @@
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
-    <row r="79" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A79" s="24" t="s">
         <v>66</v>
       </c>
@@ -27026,7 +27065,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="22" t="s">
         <v>52</v>
       </c>
@@ -27076,7 +27115,7 @@
         <v>4060.1982965341435</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="25" t="s">
         <v>2</v>
       </c>
@@ -27126,7 +27165,7 @@
         <v>115960.66341739325</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="25" t="s">
         <v>53</v>
       </c>
@@ -27176,7 +27215,7 @@
         <v>1025651.0919023927</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="25" t="s">
         <v>54</v>
       </c>
@@ -27226,7 +27265,7 @@
         <v>921665.01331325062</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="25" t="s">
         <v>55</v>
       </c>
@@ -27276,7 +27315,7 @@
         <v>563743.53274114314</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="25" t="s">
         <v>56</v>
       </c>
@@ -27326,7 +27365,7 @@
         <v>458078.37214710435</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="25" t="s">
         <v>3</v>
       </c>
@@ -27376,7 +27415,7 @@
         <v>84526.128182181987</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="29" t="s">
         <v>59</v>
       </c>
@@ -27426,19 +27465,19 @@
         <v>3173685.0000000005</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
         <v>349</v>
       </c>
@@ -27450,7 +27489,7 @@
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
         <v>344</v>
       </c>
@@ -27462,7 +27501,7 @@
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A92" s="24" t="s">
         <v>392</v>
       </c>
@@ -27512,7 +27551,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="30" t="s">
         <v>14</v>
       </c>
@@ -27562,7 +27601,7 @@
         <v>12617.766844715281</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="31" t="s">
         <v>15</v>
       </c>
@@ -27612,7 +27651,7 @@
         <v>98139.654842240081</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="31" t="s">
         <v>16</v>
       </c>
@@ -27662,7 +27701,7 @@
         <v>172631.54299830791</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="31" t="s">
         <v>17</v>
       </c>
@@ -27712,7 +27751,7 @@
         <v>57228.733856237035</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="31" t="s">
         <v>18</v>
       </c>
@@ -27762,7 +27801,7 @@
         <v>50870.550370077843</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="31" t="s">
         <v>19</v>
       </c>
@@ -27812,7 +27851,7 @@
         <v>200520.13166757469</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="31" t="s">
         <v>20</v>
       </c>
@@ -27862,7 +27901,7 @@
         <v>1844093.7906530723</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="31" t="s">
         <v>21</v>
       </c>
@@ -27912,7 +27951,7 @@
         <v>164528.03560395763</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" s="31" t="s">
         <v>22</v>
       </c>
@@ -27962,7 +28001,7 @@
         <v>61793.818114644862</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="31" t="s">
         <v>23</v>
       </c>
@@ -28012,7 +28051,7 @@
         <v>251352.05518353998</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="31" t="s">
         <v>24</v>
       </c>
@@ -28062,7 +28101,7 @@
         <v>100332.23706120817</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="31" t="s">
         <v>25</v>
       </c>
@@ -28112,7 +28151,7 @@
         <v>24301.373717603175</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="31" t="s">
         <v>26</v>
       </c>
@@ -28162,7 +28201,7 @@
         <v>82840.371125184611</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="31" t="s">
         <v>27</v>
       </c>
@@ -28212,7 +28251,7 @@
         <v>11489.456106164249</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="31" t="s">
         <v>28</v>
       </c>
@@ -28262,7 +28301,7 @@
         <v>40945.481855472186</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="29" t="s">
         <v>59</v>
       </c>
@@ -28312,89 +28351,89 @@
         <v>3173685</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
